--- a/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
@@ -2938,6 +2938,14 @@
         <v>12.119999999999999</v>
       </c>
     </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="A254" s="1">
+        <v>46387</v>
+      </c>
+      <c r="B254">
+        <v>11.640000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157500000008" bottom="0.78740157500000008" header="0.31496062000000014" footer="0.31496062000000014"/>

--- a/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>ano</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>31-11-2025</t>
+  </si>
+  <si>
+    <t>31-02-2026</t>
   </si>
 </sst>
 </file>
@@ -383,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -395,6 +398,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2940,10 +2946,18 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="1">
-        <v>46387</v>
+        <v>46053</v>
       </c>
       <c r="B254">
         <v>11.640000000000001</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="A255" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B255">
+        <v>11.43</v>
       </c>
     </row>
   </sheetData>

--- a/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
@@ -386,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -398,9 +398,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2953,11 +2950,19 @@
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="5" t="s">
+      <c r="A255" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B255">
         <v>11.43</v>
+      </c>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="A256" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B256">
+        <v>12.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/acucar_ilheus.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>ano</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>31-02-2026</t>
+  </si>
+  <si>
+    <t>31-04-2026</t>
   </si>
 </sst>
 </file>
@@ -391,13 +394,15 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -914,18 +919,19 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" style="1" width="14.42578125"/>
+    <col min="2" max="2" style="2" width="14.42578125"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>38383</v>
       </c>
       <c r="B2" s="4">
@@ -933,7 +939,7 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
@@ -941,7 +947,7 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>38442</v>
       </c>
       <c r="B4" s="4">
@@ -949,7 +955,7 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="4">
@@ -957,7 +963,7 @@
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>38503</v>
       </c>
       <c r="B6" s="4">
@@ -965,7 +971,7 @@
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="4">
@@ -973,7 +979,7 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>38564</v>
       </c>
       <c r="B8" s="4">
@@ -981,7 +987,7 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>38595</v>
       </c>
       <c r="B9" s="4">
@@ -989,7 +995,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="4">
@@ -997,7 +1003,7 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>38656</v>
       </c>
       <c r="B11" s="4">
@@ -1005,7 +1011,7 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="4">
@@ -1013,7 +1019,7 @@
       </c>
     </row>
     <row r="13" ht="12.75">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>38717</v>
       </c>
       <c r="B13" s="4">
@@ -1021,7 +1027,7 @@
       </c>
     </row>
     <row r="14" ht="12.75">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>38748</v>
       </c>
       <c r="B14" s="4">
@@ -1029,7 +1035,7 @@
       </c>
     </row>
     <row r="15" ht="12.75">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="4">
@@ -1037,7 +1043,7 @@
       </c>
     </row>
     <row r="16" ht="12.75">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>38807</v>
       </c>
       <c r="B16" s="4">
@@ -1045,7 +1051,7 @@
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="4">
@@ -1053,7 +1059,7 @@
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>38868</v>
       </c>
       <c r="B18" s="4">
@@ -1061,7 +1067,7 @@
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="4">
@@ -1069,7 +1075,7 @@
       </c>
     </row>
     <row r="20" ht="12.75">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>38929</v>
       </c>
       <c r="B20" s="4">
@@ -1077,7 +1083,7 @@
       </c>
     </row>
     <row r="21" ht="12.75">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>38960</v>
       </c>
       <c r="B21" s="4">
@@ -1085,7 +1091,7 @@
       </c>
     </row>
     <row r="22" ht="12.75">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B22" s="4">
@@ -1093,7 +1099,7 @@
       </c>
     </row>
     <row r="23" ht="12.75">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>39021</v>
       </c>
       <c r="B23" s="4">
@@ -1101,7 +1107,7 @@
       </c>
     </row>
     <row r="24" ht="12.75">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="4">
@@ -1109,7 +1115,7 @@
       </c>
     </row>
     <row r="25" ht="12.75">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>39082</v>
       </c>
       <c r="B25" s="4">
@@ -1117,7 +1123,7 @@
       </c>
     </row>
     <row r="26" ht="12.75">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>39113</v>
       </c>
       <c r="B26" s="4">
@@ -1125,7 +1131,7 @@
       </c>
     </row>
     <row r="27" ht="12.75">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="4">
@@ -1133,7 +1139,7 @@
       </c>
     </row>
     <row r="28" ht="12.75">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>39172</v>
       </c>
       <c r="B28" s="4">
@@ -1141,7 +1147,7 @@
       </c>
     </row>
     <row r="29" ht="12.75">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B29" s="4">
@@ -1149,7 +1155,7 @@
       </c>
     </row>
     <row r="30" ht="12.75">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>39233</v>
       </c>
       <c r="B30" s="4">
@@ -1157,7 +1163,7 @@
       </c>
     </row>
     <row r="31" ht="12.75">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="4">
@@ -1165,7 +1171,7 @@
       </c>
     </row>
     <row r="32" ht="12.75">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>39294</v>
       </c>
       <c r="B32" s="4">
@@ -1173,7 +1179,7 @@
       </c>
     </row>
     <row r="33" ht="12.75">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>39325</v>
       </c>
       <c r="B33" s="4">
@@ -1181,7 +1187,7 @@
       </c>
     </row>
     <row r="34" ht="12.75">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B34" s="4">
@@ -1189,7 +1195,7 @@
       </c>
     </row>
     <row r="35" ht="12.75">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>39386</v>
       </c>
       <c r="B35" s="4">
@@ -1197,7 +1203,7 @@
       </c>
     </row>
     <row r="36" ht="12.75">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B36" s="4">
@@ -1205,7 +1211,7 @@
       </c>
     </row>
     <row r="37" ht="12.75">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>39447</v>
       </c>
       <c r="B37" s="4">
@@ -1213,7 +1219,7 @@
       </c>
     </row>
     <row r="38" ht="12.75">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>39478</v>
       </c>
       <c r="B38" s="4">
@@ -1221,7 +1227,7 @@
       </c>
     </row>
     <row r="39" ht="12.75">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="4">
@@ -1229,7 +1235,7 @@
       </c>
     </row>
     <row r="40" ht="12.75">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>39538</v>
       </c>
       <c r="B40" s="4">
@@ -1237,7 +1243,7 @@
       </c>
     </row>
     <row r="41" ht="12.75">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B41" s="4">
@@ -1245,7 +1251,7 @@
       </c>
     </row>
     <row r="42" ht="12.75">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>39599</v>
       </c>
       <c r="B42" s="4">
@@ -1253,7 +1259,7 @@
       </c>
     </row>
     <row r="43" ht="12.75">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B43" s="4">
@@ -1261,7 +1267,7 @@
       </c>
     </row>
     <row r="44" ht="12.75">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>39660</v>
       </c>
       <c r="B44" s="4">
@@ -1269,7 +1275,7 @@
       </c>
     </row>
     <row r="45" ht="12.75">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>39691</v>
       </c>
       <c r="B45" s="4">
@@ -1277,7 +1283,7 @@
       </c>
     </row>
     <row r="46" ht="12.75">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B46" s="4">
@@ -1285,7 +1291,7 @@
       </c>
     </row>
     <row r="47" ht="12.75">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>39752</v>
       </c>
       <c r="B47" s="4">
@@ -1293,7 +1299,7 @@
       </c>
     </row>
     <row r="48" ht="12.75">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B48" s="4">
@@ -1301,7 +1307,7 @@
       </c>
     </row>
     <row r="49" ht="12.75">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>39813</v>
       </c>
       <c r="B49" s="4">
@@ -1309,7 +1315,7 @@
       </c>
     </row>
     <row r="50" ht="12.75">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>39844</v>
       </c>
       <c r="B50" s="4">
@@ -1317,7 +1323,7 @@
       </c>
     </row>
     <row r="51" ht="12.75">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="4">
@@ -1325,7 +1331,7 @@
       </c>
     </row>
     <row r="52" ht="12.75">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>39903</v>
       </c>
       <c r="B52" s="4">
@@ -1333,7 +1339,7 @@
       </c>
     </row>
     <row r="53" ht="12.75">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B53" s="4">
@@ -1341,7 +1347,7 @@
       </c>
     </row>
     <row r="54" ht="12.75">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>39964</v>
       </c>
       <c r="B54" s="4">
@@ -1349,7 +1355,7 @@
       </c>
     </row>
     <row r="55" ht="12.75">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B55" s="4">
@@ -1357,7 +1363,7 @@
       </c>
     </row>
     <row r="56" ht="12.75">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>40025</v>
       </c>
       <c r="B56" s="4">
@@ -1365,7 +1371,7 @@
       </c>
     </row>
     <row r="57" ht="12.75">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>40056</v>
       </c>
       <c r="B57" s="4">
@@ -1373,7 +1379,7 @@
       </c>
     </row>
     <row r="58" ht="12.75">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B58" s="4">
@@ -1381,7 +1387,7 @@
       </c>
     </row>
     <row r="59" ht="12.75">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>40117</v>
       </c>
       <c r="B59" s="4">
@@ -1389,7 +1395,7 @@
       </c>
     </row>
     <row r="60" ht="12.75">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B60" s="4">
@@ -1397,7 +1403,7 @@
       </c>
     </row>
     <row r="61" ht="12.75">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>40178</v>
       </c>
       <c r="B61" s="4">
@@ -1405,7 +1411,7 @@
       </c>
     </row>
     <row r="62" ht="12.75">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>40209</v>
       </c>
       <c r="B62" s="4">
@@ -1413,7 +1419,7 @@
       </c>
     </row>
     <row r="63" ht="12.75">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B63" s="4">
@@ -1421,7 +1427,7 @@
       </c>
     </row>
     <row r="64" ht="12.75">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>40268</v>
       </c>
       <c r="B64" s="4">
@@ -1429,7 +1435,7 @@
       </c>
     </row>
     <row r="65" ht="12.75">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B65" s="4">
@@ -1437,7 +1443,7 @@
       </c>
     </row>
     <row r="66" ht="12.75">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>40329</v>
       </c>
       <c r="B66" s="4">
@@ -1445,7 +1451,7 @@
       </c>
     </row>
     <row r="67" ht="12.75">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B67" s="4">
@@ -1453,7 +1459,7 @@
       </c>
     </row>
     <row r="68" ht="12.75">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>40390</v>
       </c>
       <c r="B68" s="4">
@@ -1461,7 +1467,7 @@
       </c>
     </row>
     <row r="69" ht="12.75">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>40421</v>
       </c>
       <c r="B69" s="4">
@@ -1469,7 +1475,7 @@
       </c>
     </row>
     <row r="70" ht="12.75">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B70" s="4">
@@ -1477,7 +1483,7 @@
       </c>
     </row>
     <row r="71" ht="12.75">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>40482</v>
       </c>
       <c r="B71" s="4">
@@ -1485,7 +1491,7 @@
       </c>
     </row>
     <row r="72" ht="12.75">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B72" s="4">
@@ -1493,7 +1499,7 @@
       </c>
     </row>
     <row r="73" ht="12.75">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>40543</v>
       </c>
       <c r="B73" s="4">
@@ -1501,7 +1507,7 @@
       </c>
     </row>
     <row r="74" ht="12.75">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>40574</v>
       </c>
       <c r="B74" s="4">
@@ -1509,7 +1515,7 @@
       </c>
     </row>
     <row r="75" ht="12.75">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B75" s="4">
@@ -1517,7 +1523,7 @@
       </c>
     </row>
     <row r="76" ht="12.75">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>40633</v>
       </c>
       <c r="B76" s="4">
@@ -1525,7 +1531,7 @@
       </c>
     </row>
     <row r="77" ht="12.75">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B77" s="4">
@@ -1533,7 +1539,7 @@
       </c>
     </row>
     <row r="78" ht="12.75">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>40694</v>
       </c>
       <c r="B78" s="4">
@@ -1541,7 +1547,7 @@
       </c>
     </row>
     <row r="79" ht="12.75">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B79" s="4">
@@ -1549,7 +1555,7 @@
       </c>
     </row>
     <row r="80" ht="12.75">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>40755</v>
       </c>
       <c r="B80" s="4">
@@ -1557,7 +1563,7 @@
       </c>
     </row>
     <row r="81" ht="12.75">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>40786</v>
       </c>
       <c r="B81" s="4">
@@ -1565,7 +1571,7 @@
       </c>
     </row>
     <row r="82" ht="12.75">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B82" s="4">
@@ -1573,7 +1579,7 @@
       </c>
     </row>
     <row r="83" ht="12.75">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>40847</v>
       </c>
       <c r="B83" s="4">
@@ -1581,7 +1587,7 @@
       </c>
     </row>
     <row r="84" ht="12.75">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B84" s="4">
@@ -1589,7 +1595,7 @@
       </c>
     </row>
     <row r="85" ht="12.75">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>40908</v>
       </c>
       <c r="B85" s="4">
@@ -1597,7 +1603,7 @@
       </c>
     </row>
     <row r="86" ht="12.75">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>40939</v>
       </c>
       <c r="B86" s="4">
@@ -1605,7 +1611,7 @@
       </c>
     </row>
     <row r="87" ht="12.75">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B87" s="4">
@@ -1613,7 +1619,7 @@
       </c>
     </row>
     <row r="88" ht="12.75">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>40999</v>
       </c>
       <c r="B88" s="4">
@@ -1621,7 +1627,7 @@
       </c>
     </row>
     <row r="89" ht="12.75">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B89" s="4">
@@ -1629,7 +1635,7 @@
       </c>
     </row>
     <row r="90" ht="12.75">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>41060</v>
       </c>
       <c r="B90" s="4">
@@ -1637,7 +1643,7 @@
       </c>
     </row>
     <row r="91" ht="12.75">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B91" s="4">
@@ -1645,7 +1651,7 @@
       </c>
     </row>
     <row r="92" ht="12.75">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>41121</v>
       </c>
       <c r="B92" s="4">
@@ -1653,7 +1659,7 @@
       </c>
     </row>
     <row r="93" ht="12.75">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>41152</v>
       </c>
       <c r="B93" s="4">
@@ -1661,7 +1667,7 @@
       </c>
     </row>
     <row r="94" ht="12.75">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B94" s="4">
@@ -1669,7 +1675,7 @@
       </c>
     </row>
     <row r="95" ht="12.75">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>41213</v>
       </c>
       <c r="B95" s="4">
@@ -1677,7 +1683,7 @@
       </c>
     </row>
     <row r="96" ht="12.75">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B96" s="4">
@@ -1685,7 +1691,7 @@
       </c>
     </row>
     <row r="97" ht="12.75">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>41274</v>
       </c>
       <c r="B97" s="4">
@@ -1693,7 +1699,7 @@
       </c>
     </row>
     <row r="98" ht="12.75">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>41305</v>
       </c>
       <c r="B98" s="4">
@@ -1701,7 +1707,7 @@
       </c>
     </row>
     <row r="99" ht="12.75">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B99" s="4">
@@ -1709,7 +1715,7 @@
       </c>
     </row>
     <row r="100" ht="12.75">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>41364</v>
       </c>
       <c r="B100" s="4">
@@ -1717,7 +1723,7 @@
       </c>
     </row>
     <row r="101" ht="12.75">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B101" s="4">
@@ -1725,7 +1731,7 @@
       </c>
     </row>
     <row r="102" ht="12.75">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>41425</v>
       </c>
       <c r="B102" s="4">
@@ -1733,7 +1739,7 @@
       </c>
     </row>
     <row r="103" ht="12.75">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B103" s="4">
@@ -1741,7 +1747,7 @@
       </c>
     </row>
     <row r="104" ht="12.75">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>41486</v>
       </c>
       <c r="B104" s="4">
@@ -1749,7 +1755,7 @@
       </c>
     </row>
     <row r="105" ht="12.75">
-      <c r="A105" s="2">
+      <c r="A105" s="3">
         <v>41517</v>
       </c>
       <c r="B105" s="4">
@@ -1757,7 +1763,7 @@
       </c>
     </row>
     <row r="106" ht="12.75">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B106" s="4">
@@ -1765,7 +1771,7 @@
       </c>
     </row>
     <row r="107" ht="12.75">
-      <c r="A107" s="2">
+      <c r="A107" s="3">
         <v>41578</v>
       </c>
       <c r="B107" s="4">
@@ -1773,7 +1779,7 @@
       </c>
     </row>
     <row r="108" ht="12.75">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B108" s="4">
@@ -1781,7 +1787,7 @@
       </c>
     </row>
     <row r="109" ht="12.75">
-      <c r="A109" s="2">
+      <c r="A109" s="3">
         <v>41639</v>
       </c>
       <c r="B109" s="4">
@@ -1789,7 +1795,7 @@
       </c>
     </row>
     <row r="110" ht="12.75">
-      <c r="A110" s="2">
+      <c r="A110" s="3">
         <v>41670</v>
       </c>
       <c r="B110" s="4">
@@ -1797,7 +1803,7 @@
       </c>
     </row>
     <row r="111" ht="12.75">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B111" s="4">
@@ -1805,7 +1811,7 @@
       </c>
     </row>
     <row r="112" ht="12.75">
-      <c r="A112" s="2">
+      <c r="A112" s="3">
         <v>41729</v>
       </c>
       <c r="B112" s="4">
@@ -1813,7 +1819,7 @@
       </c>
     </row>
     <row r="113" ht="12.75">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B113" s="4">
@@ -1821,7 +1827,7 @@
       </c>
     </row>
     <row r="114" ht="12.75">
-      <c r="A114" s="2">
+      <c r="A114" s="3">
         <v>41790</v>
       </c>
       <c r="B114" s="4">
@@ -1829,7 +1835,7 @@
       </c>
     </row>
     <row r="115" ht="12.75">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B115" s="4">
@@ -1837,7 +1843,7 @@
       </c>
     </row>
     <row r="116" ht="12.75">
-      <c r="A116" s="2">
+      <c r="A116" s="3">
         <v>41851</v>
       </c>
       <c r="B116" s="4">
@@ -1845,7 +1851,7 @@
       </c>
     </row>
     <row r="117" ht="12.75">
-      <c r="A117" s="2">
+      <c r="A117" s="3">
         <v>41882</v>
       </c>
       <c r="B117" s="4">
@@ -1853,7 +1859,7 @@
       </c>
     </row>
     <row r="118" ht="12.75">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B118" s="4">
@@ -1861,7 +1867,7 @@
       </c>
     </row>
     <row r="119" ht="12.75">
-      <c r="A119" s="2">
+      <c r="A119" s="3">
         <v>41943</v>
       </c>
       <c r="B119" s="4">
@@ -1869,7 +1875,7 @@
       </c>
     </row>
     <row r="120" ht="12.75">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B120" s="4">
@@ -1877,7 +1883,7 @@
       </c>
     </row>
     <row r="121" ht="12.75">
-      <c r="A121" s="2">
+      <c r="A121" s="3">
         <v>42004</v>
       </c>
       <c r="B121" s="4">
@@ -1885,7 +1891,7 @@
       </c>
     </row>
     <row r="122" ht="12.75">
-      <c r="A122" s="2">
+      <c r="A122" s="3">
         <v>42035</v>
       </c>
       <c r="B122" s="4">
@@ -1893,7 +1899,7 @@
       </c>
     </row>
     <row r="123" ht="12.75">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B123" s="4">
@@ -1901,7 +1907,7 @@
       </c>
     </row>
     <row r="124" ht="12.75">
-      <c r="A124" s="2">
+      <c r="A124" s="3">
         <v>42094</v>
       </c>
       <c r="B124" s="4">
@@ -1909,7 +1915,7 @@
       </c>
     </row>
     <row r="125" ht="12.75">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B125" s="4">
@@ -1917,7 +1923,7 @@
       </c>
     </row>
     <row r="126" ht="12.75">
-      <c r="A126" s="2">
+      <c r="A126" s="3">
         <v>42155</v>
       </c>
       <c r="B126" s="4">
@@ -1925,7 +1931,7 @@
       </c>
     </row>
     <row r="127" ht="12.75">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B127" s="4">
@@ -1933,7 +1939,7 @@
       </c>
     </row>
     <row r="128" ht="12.75">
-      <c r="A128" s="2">
+      <c r="A128" s="3">
         <v>42216</v>
       </c>
       <c r="B128" s="4">
@@ -1941,7 +1947,7 @@
       </c>
     </row>
     <row r="129" ht="12.75">
-      <c r="A129" s="2">
+      <c r="A129" s="3">
         <v>42247</v>
       </c>
       <c r="B129" s="4">
@@ -1949,7 +1955,7 @@
       </c>
     </row>
     <row r="130" ht="12.75">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B130" s="4">
@@ -1957,7 +1963,7 @@
       </c>
     </row>
     <row r="131" ht="12.75">
-      <c r="A131" s="2">
+      <c r="A131" s="3">
         <v>42308</v>
       </c>
       <c r="B131" s="4">
@@ -1965,7 +1971,7 @@
       </c>
     </row>
     <row r="132" ht="12.75">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B132" s="4">
@@ -1973,7 +1979,7 @@
       </c>
     </row>
     <row r="133" ht="12.75">
-      <c r="A133" s="2">
+      <c r="A133" s="3">
         <v>42369</v>
       </c>
       <c r="B133" s="4">
@@ -1981,7 +1987,7 @@
       </c>
     </row>
     <row r="134" ht="12.75">
-      <c r="A134" s="2">
+      <c r="A134" s="3">
         <v>42400</v>
       </c>
       <c r="B134" s="4">
@@ -1989,7 +1995,7 @@
       </c>
     </row>
     <row r="135" ht="12.75">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B135" s="4">
@@ -1997,7 +2003,7 @@
       </c>
     </row>
     <row r="136" ht="12.75">
-      <c r="A136" s="2">
+      <c r="A136" s="3">
         <v>42460</v>
       </c>
       <c r="B136" s="4">
@@ -2005,7 +2011,7 @@
       </c>
     </row>
     <row r="137" ht="12.75">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B137" s="4">
@@ -2013,7 +2019,7 @@
       </c>
     </row>
     <row r="138" ht="12.75">
-      <c r="A138" s="2">
+      <c r="A138" s="3">
         <v>42521</v>
       </c>
       <c r="B138" s="4">
@@ -2021,7 +2027,7 @@
       </c>
     </row>
     <row r="139" ht="12.75">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B139" s="4">
@@ -2029,7 +2035,7 @@
       </c>
     </row>
     <row r="140" ht="12.75">
-      <c r="A140" s="2">
+      <c r="A140" s="3">
         <v>42582</v>
       </c>
       <c r="B140" s="4">
@@ -2037,7 +2043,7 @@
       </c>
     </row>
     <row r="141" ht="12.75">
-      <c r="A141" s="2">
+      <c r="A141" s="3">
         <v>42613</v>
       </c>
       <c r="B141" s="4">
@@ -2045,7 +2051,7 @@
       </c>
     </row>
     <row r="142" ht="12.75">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B142" s="4">
@@ -2053,7 +2059,7 @@
       </c>
     </row>
     <row r="143" ht="12.75">
-      <c r="A143" s="2">
+      <c r="A143" s="3">
         <v>42674</v>
       </c>
       <c r="B143" s="4">
@@ -2061,7 +2067,7 @@
       </c>
     </row>
     <row r="144" ht="12.75">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B144" s="4">
@@ -2069,7 +2075,7 @@
       </c>
     </row>
     <row r="145" ht="12.75">
-      <c r="A145" s="2">
+      <c r="A145" s="3">
         <v>42735</v>
       </c>
       <c r="B145" s="4">
@@ -2077,7 +2083,7 @@
       </c>
     </row>
     <row r="146" ht="12.75">
-      <c r="A146" s="2">
+      <c r="A146" s="3">
         <v>42766</v>
       </c>
       <c r="B146" s="4">
@@ -2085,7 +2091,7 @@
       </c>
     </row>
     <row r="147" ht="12.75">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B147" s="4">
@@ -2093,7 +2099,7 @@
       </c>
     </row>
     <row r="148" ht="12.75">
-      <c r="A148" s="2">
+      <c r="A148" s="3">
         <v>42825</v>
       </c>
       <c r="B148" s="4">
@@ -2101,7 +2107,7 @@
       </c>
     </row>
     <row r="149" ht="12.75">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B149" s="4">
@@ -2109,7 +2115,7 @@
       </c>
     </row>
     <row r="150" ht="12.75">
-      <c r="A150" s="2">
+      <c r="A150" s="3">
         <v>42886</v>
       </c>
       <c r="B150" s="4">
@@ -2117,7 +2123,7 @@
       </c>
     </row>
     <row r="151" ht="12.75">
-      <c r="A151" s="2" t="s">
+      <c r="A151" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B151" s="4">
@@ -2125,7 +2131,7 @@
       </c>
     </row>
     <row r="152" ht="12.75">
-      <c r="A152" s="2">
+      <c r="A152" s="3">
         <v>42947</v>
       </c>
       <c r="B152" s="4">
@@ -2133,7 +2139,7 @@
       </c>
     </row>
     <row r="153" ht="12.75">
-      <c r="A153" s="2">
+      <c r="A153" s="3">
         <v>42978</v>
       </c>
       <c r="B153" s="4">
@@ -2141,7 +2147,7 @@
       </c>
     </row>
     <row r="154" ht="12.75">
-      <c r="A154" s="2" t="s">
+      <c r="A154" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B154" s="4">
@@ -2149,7 +2155,7 @@
       </c>
     </row>
     <row r="155" ht="12.75">
-      <c r="A155" s="2">
+      <c r="A155" s="3">
         <v>43039</v>
       </c>
       <c r="B155" s="4">
@@ -2157,7 +2163,7 @@
       </c>
     </row>
     <row r="156" ht="12.75">
-      <c r="A156" s="2" t="s">
+      <c r="A156" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B156" s="4">
@@ -2165,7 +2171,7 @@
       </c>
     </row>
     <row r="157" ht="12.75">
-      <c r="A157" s="2">
+      <c r="A157" s="3">
         <v>43100</v>
       </c>
       <c r="B157" s="4">
@@ -2173,7 +2179,7 @@
       </c>
     </row>
     <row r="158" ht="12.75">
-      <c r="A158" s="2">
+      <c r="A158" s="3">
         <v>43131</v>
       </c>
       <c r="B158" s="4">
@@ -2181,7 +2187,7 @@
       </c>
     </row>
     <row r="159" ht="12.75">
-      <c r="A159" s="2" t="s">
+      <c r="A159" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B159" s="4">
@@ -2189,7 +2195,7 @@
       </c>
     </row>
     <row r="160" ht="12.75">
-      <c r="A160" s="2">
+      <c r="A160" s="3">
         <v>43190</v>
       </c>
       <c r="B160" s="4">
@@ -2197,7 +2203,7 @@
       </c>
     </row>
     <row r="161" ht="12.75">
-      <c r="A161" s="2" t="s">
+      <c r="A161" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B161" s="4">
@@ -2205,7 +2211,7 @@
       </c>
     </row>
     <row r="162" ht="12.75">
-      <c r="A162" s="2">
+      <c r="A162" s="3">
         <v>43251</v>
       </c>
       <c r="B162" s="4">
@@ -2213,7 +2219,7 @@
       </c>
     </row>
     <row r="163" ht="12.75">
-      <c r="A163" s="2" t="s">
+      <c r="A163" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B163" s="4">
@@ -2221,7 +2227,7 @@
       </c>
     </row>
     <row r="164" ht="12.75">
-      <c r="A164" s="2">
+      <c r="A164" s="3">
         <v>43312</v>
       </c>
       <c r="B164" s="4">
@@ -2229,7 +2235,7 @@
       </c>
     </row>
     <row r="165" ht="12.75">
-      <c r="A165" s="2">
+      <c r="A165" s="3">
         <v>43343</v>
       </c>
       <c r="B165" s="4">
@@ -2237,7 +2243,7 @@
       </c>
     </row>
     <row r="166" ht="12.75">
-      <c r="A166" s="2" t="s">
+      <c r="A166" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B166" s="4">
@@ -2245,7 +2251,7 @@
       </c>
     </row>
     <row r="167" ht="12.75">
-      <c r="A167" s="2">
+      <c r="A167" s="3">
         <v>43404</v>
       </c>
       <c r="B167" s="4">
@@ -2253,7 +2259,7 @@
       </c>
     </row>
     <row r="168" ht="12.75">
-      <c r="A168" s="2" t="s">
+      <c r="A168" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B168" s="4">
@@ -2261,7 +2267,7 @@
       </c>
     </row>
     <row r="169" ht="12.75">
-      <c r="A169" s="2">
+      <c r="A169" s="3">
         <v>43465</v>
       </c>
       <c r="B169" s="4">
@@ -2269,7 +2275,7 @@
       </c>
     </row>
     <row r="170" ht="12.75">
-      <c r="A170" s="2">
+      <c r="A170" s="3">
         <v>43496</v>
       </c>
       <c r="B170" s="4">
@@ -2277,7 +2283,7 @@
       </c>
     </row>
     <row r="171" ht="12.75">
-      <c r="A171" s="2" t="s">
+      <c r="A171" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B171" s="4">
@@ -2285,7 +2291,7 @@
       </c>
     </row>
     <row r="172" ht="12.75">
-      <c r="A172" s="2">
+      <c r="A172" s="3">
         <v>43555</v>
       </c>
       <c r="B172" s="4">
@@ -2293,7 +2299,7 @@
       </c>
     </row>
     <row r="173" ht="12.75">
-      <c r="A173" s="2" t="s">
+      <c r="A173" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B173" s="4">
@@ -2301,7 +2307,7 @@
       </c>
     </row>
     <row r="174" ht="12.75">
-      <c r="A174" s="2">
+      <c r="A174" s="3">
         <v>43616</v>
       </c>
       <c r="B174" s="4">
@@ -2309,7 +2315,7 @@
       </c>
     </row>
     <row r="175" ht="12.75">
-      <c r="A175" s="2" t="s">
+      <c r="A175" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B175" s="4">
@@ -2317,7 +2323,7 @@
       </c>
     </row>
     <row r="176" ht="12.75">
-      <c r="A176" s="2">
+      <c r="A176" s="3">
         <v>43677</v>
       </c>
       <c r="B176" s="4">
@@ -2325,7 +2331,7 @@
       </c>
     </row>
     <row r="177" ht="12.75">
-      <c r="A177" s="2">
+      <c r="A177" s="3">
         <v>43708</v>
       </c>
       <c r="B177" s="4">
@@ -2333,7 +2339,7 @@
       </c>
     </row>
     <row r="178" ht="12.75">
-      <c r="A178" s="2" t="s">
+      <c r="A178" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B178" s="4">
@@ -2341,7 +2347,7 @@
       </c>
     </row>
     <row r="179" ht="12.75">
-      <c r="A179" s="2">
+      <c r="A179" s="3">
         <v>43769</v>
       </c>
       <c r="B179" s="4">
@@ -2349,7 +2355,7 @@
       </c>
     </row>
     <row r="180" ht="12.75">
-      <c r="A180" s="2" t="s">
+      <c r="A180" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B180" s="4">
@@ -2357,7 +2363,7 @@
       </c>
     </row>
     <row r="181" ht="12.75">
-      <c r="A181" s="2">
+      <c r="A181" s="3">
         <v>43830</v>
       </c>
       <c r="B181" s="4">
@@ -2365,7 +2371,7 @@
       </c>
     </row>
     <row r="182" ht="12.75">
-      <c r="A182" s="2">
+      <c r="A182" s="3">
         <v>43861</v>
       </c>
       <c r="B182" s="4">
@@ -2373,7 +2379,7 @@
       </c>
     </row>
     <row r="183" ht="12.75">
-      <c r="A183" s="2" t="s">
+      <c r="A183" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B183" s="4">
@@ -2381,7 +2387,7 @@
       </c>
     </row>
     <row r="184" ht="12.75">
-      <c r="A184" s="2">
+      <c r="A184" s="3">
         <v>43921</v>
       </c>
       <c r="B184" s="4">
@@ -2389,7 +2395,7 @@
       </c>
     </row>
     <row r="185" ht="12.75">
-      <c r="A185" s="2" t="s">
+      <c r="A185" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B185" s="4">
@@ -2397,7 +2403,7 @@
       </c>
     </row>
     <row r="186" ht="12.75">
-      <c r="A186" s="2">
+      <c r="A186" s="3">
         <v>43982</v>
       </c>
       <c r="B186" s="4">
@@ -2405,7 +2411,7 @@
       </c>
     </row>
     <row r="187" ht="12.75">
-      <c r="A187" s="2" t="s">
+      <c r="A187" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B187" s="4">
@@ -2413,7 +2419,7 @@
       </c>
     </row>
     <row r="188" ht="12.75">
-      <c r="A188" s="2">
+      <c r="A188" s="3">
         <v>44043</v>
       </c>
       <c r="B188" s="4">
@@ -2421,7 +2427,7 @@
       </c>
     </row>
     <row r="189" ht="12.75">
-      <c r="A189" s="2">
+      <c r="A189" s="3">
         <v>44074</v>
       </c>
       <c r="B189" s="4">
@@ -2429,7 +2435,7 @@
       </c>
     </row>
     <row r="190" ht="12.75">
-      <c r="A190" s="2" t="s">
+      <c r="A190" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B190" s="4">
@@ -2437,7 +2443,7 @@
       </c>
     </row>
     <row r="191" ht="12.75">
-      <c r="A191" s="2">
+      <c r="A191" s="3">
         <v>44135</v>
       </c>
       <c r="B191" s="4">
@@ -2445,7 +2451,7 @@
       </c>
     </row>
     <row r="192" ht="12.75">
-      <c r="A192" s="2" t="s">
+      <c r="A192" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B192" s="4">
@@ -2453,7 +2459,7 @@
       </c>
     </row>
     <row r="193" ht="12.75">
-      <c r="A193" s="2">
+      <c r="A193" s="3">
         <v>44196</v>
       </c>
       <c r="B193" s="4">
@@ -2461,7 +2467,7 @@
       </c>
     </row>
     <row r="194" ht="12.75">
-      <c r="A194" s="2">
+      <c r="A194" s="3">
         <v>44227</v>
       </c>
       <c r="B194" s="4">
@@ -2469,7 +2475,7 @@
       </c>
     </row>
     <row r="195" ht="12.75">
-      <c r="A195" s="2" t="s">
+      <c r="A195" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B195" s="4">
@@ -2477,7 +2483,7 @@
       </c>
     </row>
     <row r="196" ht="12.75">
-      <c r="A196" s="2">
+      <c r="A196" s="3">
         <v>44286</v>
       </c>
       <c r="B196" s="4">
@@ -2485,7 +2491,7 @@
       </c>
     </row>
     <row r="197" ht="12.75">
-      <c r="A197" s="2" t="s">
+      <c r="A197" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B197" s="4">
@@ -2493,7 +2499,7 @@
       </c>
     </row>
     <row r="198" ht="12.75">
-      <c r="A198" s="2">
+      <c r="A198" s="3">
         <v>44347</v>
       </c>
       <c r="B198" s="4">
@@ -2501,7 +2507,7 @@
       </c>
     </row>
     <row r="199" ht="12.75">
-      <c r="A199" s="2" t="s">
+      <c r="A199" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B199" s="4">
@@ -2509,7 +2515,7 @@
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="2">
+      <c r="A200" s="3">
         <v>44408</v>
       </c>
       <c r="B200" s="4">
@@ -2550,7 +2556,7 @@
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="2">
+      <c r="A205" s="3">
         <v>44561</v>
       </c>
       <c r="B205" s="4">
@@ -2881,7 +2887,7 @@
       <c r="A246" s="1">
         <v>45808</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="2">
         <v>14.01</v>
       </c>
     </row>
@@ -2937,7 +2943,7 @@
       <c r="A253" s="1">
         <v>46022</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="2">
         <v>12.119999999999999</v>
       </c>
     </row>
@@ -2945,7 +2951,7 @@
       <c r="A254" s="1">
         <v>46053</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="2">
         <v>11.640000000000001</v>
       </c>
     </row>
@@ -2953,7 +2959,7 @@
       <c r="A255" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="2">
         <v>11.43</v>
       </c>
     </row>
@@ -2961,8 +2967,16 @@
       <c r="A256" s="1">
         <v>46112</v>
       </c>
-      <c r="B256">
+      <c r="B256" s="2">
         <v>12.15</v>
+      </c>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="A257" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B257" s="2">
+        <v>11.52</v>
       </c>
     </row>
   </sheetData>
